--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261022.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261022.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,451,994</t>
+          <t>72,602,866</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>72,602,866</t>
+          <t>7,451,994</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,094,535</t>
+          <t>31,023,081</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>31,023,081</t>
+          <t>2,094,535</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
